--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,9 +413,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>172501 - Inserção de textos, desenhos e outros materiais de propaganda e publicidade, em qualquer meio (excet</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,23 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>172501 - Inserção de textos, desenhos e outros materiais de propaganda e publicidade, em qualquer meio (excet</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,9 +413,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>240102 - Serviços de placas, sinalização visual, banners, adesivos e congêneres.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,6 +431,21 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr"/>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>071001 - Limpeza, manutenção e conservação de vias e logradouros públicos, parques, jardins e congêneres.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>240102 - Serviços de placas, sinalização visual, banners, adesivos e congêneres.</t>
+          <t>071001 - Limpeza, manutenção e conservação de vias e logradouros públicos, parques, jardins e congêneres.</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -431,21 +431,6 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr"/>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>071001 - Limpeza, manutenção e conservação de vias e logradouros públicos, parques, jardins e congêneres.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,25 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>071001 - Limpeza, manutenção e conservação de vias e logradouros públicos, parques, jardins e congêneres.</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,9 +413,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>110401 - Armazenamento, depósito, guarda de bens de qualquer espécie.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,6 +431,21 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr"/>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>172001 - Consultoria e assessoria econômica ou financeira.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,21 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>171901 - Contabilidade, inclusive serviços técnicos e auxiliares.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6 +461,21 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>140201 - Assistência técnica.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,21 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>070202 - Execução, por empreitada ou subempreitada, de obras de construção civil, hidráulica ou elétrica e de outras obras semelhantes, inclusive sondagem, perfuração de poços, escavação, drenagem e irrigação, terraplanagem, pavimentação, concretagem e a instalação e montagem de produtos, peças e equipamentos (exceto o fornecimento de mercadorias produzidas pelo prestador de serviços fora do local da prestação dos serviços, que fica sujeito ao ICMS).</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,6 +491,21 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>010501 - Licenciamento ou cessão de direito de uso de programas de computação.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,21 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>071301 - Dedetização, desinfecção, desinsetização, imunização, higienização, desratização, pulverização e congêneres.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,6 +521,21 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>170303 - Planejamento, coordenação, programação ou organização administrativa.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,6 +536,36 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>140101 - Lubrificação, limpeza, lustração, revisão, carga e recarga, conserto, restauração, blindagem, manutenção e conservação de máquinas, veículos, aparelhos, equipamentos, motores, elevadores ou de qualquer objeto (exceto peças e partes empregadas, que ficam sujeitas ao ICMS).</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>170201 - Datilografia, digitação, estenografia e congêneres.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +566,21 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>070901 - VARRIÇÃO, COLETA, REMOÇÃO, INCINERAÇÃO, TRATAMENTO, RECICLAGEM, SEPARAÇÃO E DESTINAÇÃO FINAL DE LIXO, REJEITOS E OUTROS RESÍDUOS QUAISQUER.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,6 +581,21 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>170101 - Assessoria ou consultoria de qualquer natureza, não contida em outros itens desta lista.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,6 +596,21 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>010601 - Assessoria e consultoria em informática.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,6 +611,21 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>042201 - Planos de medicina de grupo ou individual e convênios para prestação de assistência médica, hospitalar, odontológica e congêneres.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,6 +626,21 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>171401 - Advocacia</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -641,6 +641,21 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>171201 - Administração em geral, inclusive de bens e negócios de terceiros.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,6 +656,21 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>010701 - Suporte técnico em informática, inclusive instalação, configuração e manutenção de programas de computação e bancos de dados.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_272.xlsx
+++ b/planos_empresas/plano_empresa_272.xlsx
@@ -422,11 +422,7 @@
           <t>110401 - Armazenamento, depósito, guarda de bens de qualquer espécie.</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B1" t="inlineStr"/>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr"/>
@@ -437,11 +433,7 @@
           <t>172001 - Consultoria e assessoria econômica ou financeira.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -452,11 +444,7 @@
           <t>171901 - Contabilidade, inclusive serviços técnicos e auxiliares.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,11 +455,7 @@
           <t>140201 - Assistência técnica.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -482,11 +466,7 @@
           <t>070202 - Execução, por empreitada ou subempreitada, de obras de construção civil, hidráulica ou elétrica e de outras obras semelhantes, inclusive sondagem, perfuração de poços, escavação, drenagem e irrigação, terraplanagem, pavimentação, concretagem e a instalação e montagem de produtos, peças e equipamentos (exceto o fornecimento de mercadorias produzidas pelo prestador de serviços fora do local da prestação dos serviços, que fica sujeito ao ICMS).</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -497,11 +477,7 @@
           <t>010501 - Licenciamento ou cessão de direito de uso de programas de computação.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -512,11 +488,7 @@
           <t>071301 - Dedetização, desinfecção, desinsetização, imunização, higienização, desratização, pulverização e congêneres.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -527,11 +499,7 @@
           <t>170303 - Planejamento, coordenação, programação ou organização administrativa.</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -542,11 +510,7 @@
           <t>140101 - Lubrificação, limpeza, lustração, revisão, carga e recarga, conserto, restauração, blindagem, manutenção e conservação de máquinas, veículos, aparelhos, equipamentos, motores, elevadores ou de qualquer objeto (exceto peças e partes empregadas, que ficam sujeitas ao ICMS).</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -557,11 +521,7 @@
           <t>170201 - Datilografia, digitação, estenografia e congêneres.</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -572,11 +532,7 @@
           <t>070901 - VARRIÇÃO, COLETA, REMOÇÃO, INCINERAÇÃO, TRATAMENTO, RECICLAGEM, SEPARAÇÃO E DESTINAÇÃO FINAL DE LIXO, REJEITOS E OUTROS RESÍDUOS QUAISQUER.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -587,11 +543,7 @@
           <t>170101 - Assessoria ou consultoria de qualquer natureza, não contida em outros itens desta lista.</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -602,11 +554,7 @@
           <t>010601 - Assessoria e consultoria em informática.</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -617,11 +565,7 @@
           <t>042201 - Planos de medicina de grupo ou individual e convênios para prestação de assistência médica, hospitalar, odontológica e congêneres.</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -632,11 +576,7 @@
           <t>171401 - Advocacia</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -647,11 +587,7 @@
           <t>171201 - Administração em geral, inclusive de bens e negócios de terceiros.</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -662,11 +598,7 @@
           <t>010701 - Suporte técnico em informática, inclusive instalação, configuração e manutenção de programas de computação e bancos de dados.</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
